--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467439</v>
+        <v>124467435</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514824</v>
+        <v>514733</v>
       </c>
       <c r="R2" t="n">
-        <v>7092689</v>
+        <v>7092818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467424</v>
+        <v>124467437</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514760</v>
+        <v>514859</v>
       </c>
       <c r="R3" t="n">
-        <v>7092670</v>
+        <v>7092793</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467438</v>
+        <v>124467433</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514966</v>
+        <v>514736</v>
       </c>
       <c r="R4" t="n">
-        <v>7092776</v>
+        <v>7092656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467433</v>
+        <v>124467425</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514736</v>
+        <v>514868</v>
       </c>
       <c r="R5" t="n">
-        <v>7092656</v>
+        <v>7092732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467440</v>
+        <v>124467427</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514991</v>
+        <v>514840</v>
       </c>
       <c r="R6" t="n">
-        <v>7092891</v>
+        <v>7092768</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467427</v>
+        <v>124467440</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514840</v>
+        <v>514991</v>
       </c>
       <c r="R7" t="n">
-        <v>7092768</v>
+        <v>7092891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467442</v>
+        <v>124467423</v>
       </c>
       <c r="B9" t="n">
-        <v>91579</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515001</v>
+        <v>514889</v>
       </c>
       <c r="R9" t="n">
-        <v>7092701</v>
+        <v>7092670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467425</v>
+        <v>124467439</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514868</v>
+        <v>514824</v>
       </c>
       <c r="R10" t="n">
-        <v>7092732</v>
+        <v>7092689</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467423</v>
+        <v>124467431</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514889</v>
+        <v>514768</v>
       </c>
       <c r="R11" t="n">
-        <v>7092670</v>
+        <v>7092696</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,11 +1679,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467421</v>
+        <v>124467424</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1846,24 +1841,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514988</v>
+        <v>514760</v>
       </c>
       <c r="R13" t="n">
-        <v>7092790</v>
+        <v>7092670</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467428</v>
+        <v>124467441</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514789</v>
+        <v>514761</v>
       </c>
       <c r="R14" t="n">
-        <v>7092786</v>
+        <v>7092662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2029,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467437</v>
+        <v>124467417</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514859</v>
+        <v>514963</v>
       </c>
       <c r="R15" t="n">
-        <v>7092793</v>
+        <v>7092735</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467441</v>
+        <v>124467428</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514761</v>
+        <v>514789</v>
       </c>
       <c r="R16" t="n">
-        <v>7092662</v>
+        <v>7092786</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2238,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467431</v>
+        <v>124467422</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2254,34 +2241,54 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514768</v>
+        <v>514980</v>
       </c>
       <c r="R17" t="n">
-        <v>7092696</v>
+        <v>7092787</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,6 +2321,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2340,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467426</v>
+        <v>124467442</v>
       </c>
       <c r="B18" t="n">
-        <v>91023</v>
+        <v>91579</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,25 +2364,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>760</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2380,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514767</v>
+        <v>515001</v>
       </c>
       <c r="R18" t="n">
-        <v>7092693</v>
+        <v>7092701</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467422</v>
+        <v>124467432</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2458,54 +2470,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514980</v>
+        <v>514748</v>
       </c>
       <c r="R19" t="n">
-        <v>7092787</v>
+        <v>7092677</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2538,11 +2530,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2569,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467432</v>
+        <v>124467421</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2585,34 +2572,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514748</v>
+        <v>514988</v>
       </c>
       <c r="R20" t="n">
-        <v>7092677</v>
+        <v>7092790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,6 +2640,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2671,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467417</v>
+        <v>124467426</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>91023</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2683,25 +2683,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514963</v>
+        <v>514767</v>
       </c>
       <c r="R21" t="n">
-        <v>7092735</v>
+        <v>7092693</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467434</v>
+        <v>124467438</v>
       </c>
       <c r="B22" t="n">
         <v>79891</v>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514740</v>
+        <v>514966</v>
       </c>
       <c r="R22" t="n">
-        <v>7092648</v>
+        <v>7092776</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467435</v>
+        <v>124467434</v>
       </c>
       <c r="B23" t="n">
         <v>79891</v>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514733</v>
+        <v>514740</v>
       </c>
       <c r="R23" t="n">
-        <v>7092818</v>
+        <v>7092648</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467435</v>
+        <v>124467439</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514733</v>
+        <v>514824</v>
       </c>
       <c r="R2" t="n">
-        <v>7092818</v>
+        <v>7092689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467437</v>
+        <v>124467434</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514859</v>
+        <v>514740</v>
       </c>
       <c r="R3" t="n">
-        <v>7092793</v>
+        <v>7092648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467433</v>
+        <v>124467421</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514736</v>
+        <v>514988</v>
       </c>
       <c r="R4" t="n">
-        <v>7092656</v>
+        <v>7092790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467425</v>
+        <v>124467424</v>
       </c>
       <c r="B5" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514868</v>
+        <v>514760</v>
       </c>
       <c r="R5" t="n">
-        <v>7092732</v>
+        <v>7092670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1070,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467427</v>
+        <v>124467437</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1123,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514840</v>
+        <v>514859</v>
       </c>
       <c r="R6" t="n">
-        <v>7092768</v>
+        <v>7092793</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467440</v>
+        <v>124467430</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514991</v>
+        <v>514973</v>
       </c>
       <c r="R7" t="n">
-        <v>7092891</v>
+        <v>7092718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,11 +1279,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467429</v>
+        <v>124467432</v>
       </c>
       <c r="B8" t="n">
         <v>79891</v>
@@ -1332,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514740</v>
+        <v>514748</v>
       </c>
       <c r="R8" t="n">
-        <v>7092800</v>
+        <v>7092677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467423</v>
+        <v>124467438</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514889</v>
+        <v>514966</v>
       </c>
       <c r="R9" t="n">
-        <v>7092670</v>
+        <v>7092776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,11 +1483,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467439</v>
+        <v>124467423</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514824</v>
+        <v>514889</v>
       </c>
       <c r="R10" t="n">
-        <v>7092689</v>
+        <v>7092670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,6 +1585,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,7 +1616,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467431</v>
+        <v>124467435</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1643,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514768</v>
+        <v>514733</v>
       </c>
       <c r="R11" t="n">
-        <v>7092696</v>
+        <v>7092818</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1718,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467430</v>
+        <v>124467431</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1745,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514973</v>
+        <v>514768</v>
       </c>
       <c r="R12" t="n">
-        <v>7092718</v>
+        <v>7092696</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467424</v>
+        <v>124467427</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1836,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514760</v>
+        <v>514840</v>
       </c>
       <c r="R13" t="n">
-        <v>7092670</v>
+        <v>7092768</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,11 +1896,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467441</v>
+        <v>124467417</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1938,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514761</v>
+        <v>514963</v>
       </c>
       <c r="R14" t="n">
-        <v>7092662</v>
+        <v>7092735</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,11 +1998,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467417</v>
+        <v>124467442</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91579</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2036,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514963</v>
+        <v>515001</v>
       </c>
       <c r="R15" t="n">
-        <v>7092735</v>
+        <v>7092701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467428</v>
+        <v>124467425</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2138,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514789</v>
+        <v>514868</v>
       </c>
       <c r="R16" t="n">
-        <v>7092786</v>
+        <v>7092732</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467422</v>
+        <v>124467433</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,54 +2244,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514980</v>
+        <v>514736</v>
       </c>
       <c r="R17" t="n">
-        <v>7092787</v>
+        <v>7092656</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,11 +2304,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467442</v>
+        <v>124467440</v>
       </c>
       <c r="B18" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,25 +2342,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515001</v>
+        <v>514991</v>
       </c>
       <c r="R18" t="n">
-        <v>7092701</v>
+        <v>7092891</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,6 +2406,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467432</v>
+        <v>124467426</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2466,25 +2449,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514748</v>
+        <v>514767</v>
       </c>
       <c r="R19" t="n">
-        <v>7092677</v>
+        <v>7092693</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,7 +2539,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467421</v>
+        <v>124467422</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2589,25 +2572,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514988</v>
+        <v>514980</v>
       </c>
       <c r="R20" t="n">
-        <v>7092790</v>
+        <v>7092787</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2644,7 +2639,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2671,10 +2666,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467426</v>
+        <v>124467441</v>
       </c>
       <c r="B21" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2683,25 +2678,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2711,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514767</v>
+        <v>514761</v>
       </c>
       <c r="R21" t="n">
-        <v>7092693</v>
+        <v>7092662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2747,6 +2742,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2773,7 +2773,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467438</v>
+        <v>124467428</v>
       </c>
       <c r="B22" t="n">
         <v>79891</v>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514966</v>
+        <v>514789</v>
       </c>
       <c r="R22" t="n">
-        <v>7092776</v>
+        <v>7092786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467434</v>
+        <v>124467429</v>
       </c>
       <c r="B23" t="n">
         <v>79891</v>
@@ -2918,7 +2918,7 @@
         <v>514740</v>
       </c>
       <c r="R23" t="n">
-        <v>7092648</v>
+        <v>7092800</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467439</v>
+        <v>124467435</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514824</v>
+        <v>514733</v>
       </c>
       <c r="R2" t="n">
-        <v>7092689</v>
+        <v>7092818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467434</v>
+        <v>124467428</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514740</v>
+        <v>514789</v>
       </c>
       <c r="R3" t="n">
-        <v>7092648</v>
+        <v>7092786</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467421</v>
+        <v>124467440</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514988</v>
+        <v>514991</v>
       </c>
       <c r="R4" t="n">
-        <v>7092790</v>
+        <v>7092891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467424</v>
+        <v>124467421</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1028,16 +1020,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514760</v>
+        <v>514988</v>
       </c>
       <c r="R5" t="n">
-        <v>7092670</v>
+        <v>7092790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467437</v>
+        <v>124467426</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514859</v>
+        <v>514767</v>
       </c>
       <c r="R6" t="n">
-        <v>7092793</v>
+        <v>7092693</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467430</v>
+        <v>124467442</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514973</v>
+        <v>515001</v>
       </c>
       <c r="R7" t="n">
-        <v>7092718</v>
+        <v>7092701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467432</v>
+        <v>124467430</v>
       </c>
       <c r="B8" t="n">
         <v>79891</v>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514748</v>
+        <v>514973</v>
       </c>
       <c r="R8" t="n">
-        <v>7092677</v>
+        <v>7092718</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467438</v>
+        <v>124467432</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514966</v>
+        <v>514748</v>
       </c>
       <c r="R9" t="n">
-        <v>7092776</v>
+        <v>7092677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467423</v>
+        <v>124467433</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514889</v>
+        <v>514736</v>
       </c>
       <c r="R10" t="n">
-        <v>7092670</v>
+        <v>7092656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,11 +1585,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467435</v>
+        <v>124467423</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,21 +1627,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514733</v>
+        <v>514889</v>
       </c>
       <c r="R11" t="n">
-        <v>7092818</v>
+        <v>7092670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,6 +1687,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,7 +1718,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467431</v>
+        <v>124467427</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514768</v>
+        <v>514840</v>
       </c>
       <c r="R12" t="n">
-        <v>7092696</v>
+        <v>7092768</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467427</v>
+        <v>124467417</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514840</v>
+        <v>514963</v>
       </c>
       <c r="R13" t="n">
-        <v>7092768</v>
+        <v>7092735</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467417</v>
+        <v>124467422</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1938,34 +1938,54 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514963</v>
+        <v>514980</v>
       </c>
       <c r="R14" t="n">
-        <v>7092735</v>
+        <v>7092787</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,6 +2018,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467442</v>
+        <v>124467429</v>
       </c>
       <c r="B15" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,25 +2061,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2064,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515001</v>
+        <v>514740</v>
       </c>
       <c r="R15" t="n">
-        <v>7092701</v>
+        <v>7092800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467425</v>
+        <v>124467437</v>
       </c>
       <c r="B16" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,25 +2163,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514868</v>
+        <v>514859</v>
       </c>
       <c r="R16" t="n">
-        <v>7092732</v>
+        <v>7092793</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,10 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467433</v>
+        <v>124467425</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,25 +2265,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514736</v>
+        <v>514868</v>
       </c>
       <c r="R17" t="n">
-        <v>7092656</v>
+        <v>7092732</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,10 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467440</v>
+        <v>124467424</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2346,21 +2371,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2370,10 +2395,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514991</v>
+        <v>514760</v>
       </c>
       <c r="R18" t="n">
-        <v>7092891</v>
+        <v>7092670</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,7 +2435,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467426</v>
+        <v>124467439</v>
       </c>
       <c r="B19" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,25 +2474,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514767</v>
+        <v>514824</v>
       </c>
       <c r="R19" t="n">
-        <v>7092693</v>
+        <v>7092689</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,10 +2564,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467422</v>
+        <v>124467441</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,54 +2580,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514980</v>
+        <v>514761</v>
       </c>
       <c r="R20" t="n">
-        <v>7092787</v>
+        <v>7092662</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2639,7 +2644,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2666,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467441</v>
+        <v>124467438</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2682,21 +2687,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2706,10 +2711,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514761</v>
+        <v>514966</v>
       </c>
       <c r="R21" t="n">
-        <v>7092662</v>
+        <v>7092776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,11 +2747,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2773,7 +2773,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467428</v>
+        <v>124467431</v>
       </c>
       <c r="B22" t="n">
         <v>79891</v>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514789</v>
+        <v>514768</v>
       </c>
       <c r="R22" t="n">
-        <v>7092786</v>
+        <v>7092696</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467429</v>
+        <v>124467434</v>
       </c>
       <c r="B23" t="n">
         <v>79891</v>
@@ -2918,7 +2918,7 @@
         <v>514740</v>
       </c>
       <c r="R23" t="n">
-        <v>7092800</v>
+        <v>7092648</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467435</v>
+        <v>124467417</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514733</v>
+        <v>514963</v>
       </c>
       <c r="R2" t="n">
-        <v>7092818</v>
+        <v>7092735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467428</v>
+        <v>124467438</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514789</v>
+        <v>514966</v>
       </c>
       <c r="R3" t="n">
-        <v>7092786</v>
+        <v>7092776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467440</v>
+        <v>124467429</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514991</v>
+        <v>514740</v>
       </c>
       <c r="R4" t="n">
-        <v>7092891</v>
+        <v>7092800</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1101,7 +1096,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467426</v>
+        <v>124467425</v>
       </c>
       <c r="B6" t="n">
         <v>91023</v>
@@ -1141,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514767</v>
+        <v>514868</v>
       </c>
       <c r="R6" t="n">
-        <v>7092693</v>
+        <v>7092732</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467442</v>
+        <v>124467426</v>
       </c>
       <c r="B7" t="n">
-        <v>91579</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515001</v>
+        <v>514767</v>
       </c>
       <c r="R7" t="n">
-        <v>7092701</v>
+        <v>7092693</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467430</v>
+        <v>124467422</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,34 +1316,54 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514973</v>
+        <v>514980</v>
       </c>
       <c r="R8" t="n">
-        <v>7092718</v>
+        <v>7092787</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,6 +1396,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467432</v>
+        <v>124467441</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514748</v>
+        <v>514761</v>
       </c>
       <c r="R9" t="n">
-        <v>7092677</v>
+        <v>7092662</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,6 +1503,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,7 +1636,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467423</v>
+        <v>124467424</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1651,7 +1676,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514889</v>
+        <v>514760</v>
       </c>
       <c r="R11" t="n">
         <v>7092670</v>
@@ -1718,7 +1743,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467427</v>
+        <v>124467435</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1758,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514840</v>
+        <v>514733</v>
       </c>
       <c r="R12" t="n">
-        <v>7092768</v>
+        <v>7092818</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467417</v>
+        <v>124467428</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,21 +1861,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1860,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514963</v>
+        <v>514789</v>
       </c>
       <c r="R13" t="n">
-        <v>7092735</v>
+        <v>7092786</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467422</v>
+        <v>124467434</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1938,54 +1963,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514980</v>
+        <v>514740</v>
       </c>
       <c r="R14" t="n">
-        <v>7092787</v>
+        <v>7092648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2018,11 +2023,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,7 +2049,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467429</v>
+        <v>124467427</v>
       </c>
       <c r="B15" t="n">
         <v>79891</v>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514740</v>
+        <v>514840</v>
       </c>
       <c r="R15" t="n">
-        <v>7092800</v>
+        <v>7092768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467437</v>
+        <v>124467430</v>
       </c>
       <c r="B16" t="n">
         <v>79891</v>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514859</v>
+        <v>514973</v>
       </c>
       <c r="R16" t="n">
-        <v>7092793</v>
+        <v>7092718</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467425</v>
+        <v>124467423</v>
       </c>
       <c r="B17" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2265,25 +2265,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514868</v>
+        <v>514889</v>
       </c>
       <c r="R17" t="n">
-        <v>7092732</v>
+        <v>7092670</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2329,6 +2329,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,10 +2360,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467424</v>
+        <v>124467440</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2371,21 +2376,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2395,10 +2400,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514760</v>
+        <v>514991</v>
       </c>
       <c r="R18" t="n">
-        <v>7092670</v>
+        <v>7092891</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2435,7 +2440,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,10 +2467,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467439</v>
+        <v>124467442</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2474,25 +2479,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2507,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514824</v>
+        <v>515001</v>
       </c>
       <c r="R19" t="n">
-        <v>7092689</v>
+        <v>7092701</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,10 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467441</v>
+        <v>124467437</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,21 +2585,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2609,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514761</v>
+        <v>514859</v>
       </c>
       <c r="R20" t="n">
-        <v>7092662</v>
+        <v>7092793</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2640,11 +2645,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2671,7 +2671,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467438</v>
+        <v>124467431</v>
       </c>
       <c r="B21" t="n">
         <v>79891</v>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514966</v>
+        <v>514768</v>
       </c>
       <c r="R21" t="n">
-        <v>7092776</v>
+        <v>7092696</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467431</v>
+        <v>124467439</v>
       </c>
       <c r="B22" t="n">
         <v>79891</v>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514768</v>
+        <v>514824</v>
       </c>
       <c r="R22" t="n">
-        <v>7092696</v>
+        <v>7092689</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467434</v>
+        <v>124467432</v>
       </c>
       <c r="B23" t="n">
         <v>79891</v>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514740</v>
+        <v>514748</v>
       </c>
       <c r="R23" t="n">
-        <v>7092648</v>
+        <v>7092677</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467421</v>
+        <v>124467425</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,46 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514988</v>
+        <v>514868</v>
       </c>
       <c r="R5" t="n">
-        <v>7092790</v>
+        <v>7092732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467425</v>
+        <v>124467421</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,38 +1095,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514868</v>
+        <v>514988</v>
       </c>
       <c r="R6" t="n">
-        <v>7092732</v>
+        <v>7092790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,6 +1167,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467433</v>
+        <v>124467424</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,21 +1550,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514736</v>
+        <v>514760</v>
       </c>
       <c r="R10" t="n">
-        <v>7092656</v>
+        <v>7092670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,6 +1610,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467424</v>
+        <v>124467433</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,21 +1657,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514760</v>
+        <v>514736</v>
       </c>
       <c r="R11" t="n">
-        <v>7092670</v>
+        <v>7092656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,11 +1717,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467417</v>
+        <v>124467431</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514963</v>
+        <v>514768</v>
       </c>
       <c r="R2" t="n">
-        <v>7092735</v>
+        <v>7092696</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467438</v>
+        <v>124467439</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514966</v>
+        <v>514824</v>
       </c>
       <c r="R3" t="n">
-        <v>7092776</v>
+        <v>7092689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467429</v>
+        <v>124467438</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514740</v>
+        <v>514966</v>
       </c>
       <c r="R4" t="n">
-        <v>7092800</v>
+        <v>7092776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467425</v>
+        <v>124467430</v>
       </c>
       <c r="B5" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514868</v>
+        <v>514973</v>
       </c>
       <c r="R5" t="n">
-        <v>7092732</v>
+        <v>7092718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467421</v>
+        <v>124467432</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,42 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514988</v>
+        <v>514748</v>
       </c>
       <c r="R6" t="n">
-        <v>7092790</v>
+        <v>7092677</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467426</v>
+        <v>124467422</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,38 +1197,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514767</v>
+        <v>514980</v>
       </c>
       <c r="R7" t="n">
-        <v>7092693</v>
+        <v>7092787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467422</v>
+        <v>124467434</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,54 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514980</v>
+        <v>514740</v>
       </c>
       <c r="R8" t="n">
-        <v>7092787</v>
+        <v>7092648</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467441</v>
+        <v>124467435</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514761</v>
+        <v>514733</v>
       </c>
       <c r="R9" t="n">
-        <v>7092662</v>
+        <v>7092818</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467424</v>
+        <v>124467433</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514760</v>
+        <v>514736</v>
       </c>
       <c r="R10" t="n">
-        <v>7092670</v>
+        <v>7092656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467433</v>
+        <v>124467437</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1681,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514736</v>
+        <v>514859</v>
       </c>
       <c r="R11" t="n">
-        <v>7092656</v>
+        <v>7092793</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467435</v>
+        <v>124467421</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,34 +1736,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514733</v>
+        <v>514988</v>
       </c>
       <c r="R12" t="n">
-        <v>7092818</v>
+        <v>7092790</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,6 +1804,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,7 +1835,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467428</v>
+        <v>124467427</v>
       </c>
       <c r="B13" t="n">
         <v>79891</v>
@@ -1885,10 +1875,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514789</v>
+        <v>514840</v>
       </c>
       <c r="R13" t="n">
-        <v>7092786</v>
+        <v>7092768</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467434</v>
+        <v>124467423</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1953,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514740</v>
+        <v>514889</v>
       </c>
       <c r="R14" t="n">
-        <v>7092648</v>
+        <v>7092670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,6 +2013,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,7 +2044,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467427</v>
+        <v>124467428</v>
       </c>
       <c r="B15" t="n">
         <v>79891</v>
@@ -2089,10 +2084,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514840</v>
+        <v>514789</v>
       </c>
       <c r="R15" t="n">
-        <v>7092768</v>
+        <v>7092786</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2146,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467430</v>
+        <v>124467442</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,25 +2158,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2191,10 +2186,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514973</v>
+        <v>515001</v>
       </c>
       <c r="R16" t="n">
-        <v>7092718</v>
+        <v>7092701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2248,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467423</v>
+        <v>124467424</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2293,7 +2288,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514889</v>
+        <v>514760</v>
       </c>
       <c r="R17" t="n">
         <v>7092670</v>
@@ -2467,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467442</v>
+        <v>124467425</v>
       </c>
       <c r="B19" t="n">
-        <v>91579</v>
+        <v>91023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,25 +2474,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2507,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515001</v>
+        <v>514868</v>
       </c>
       <c r="R19" t="n">
-        <v>7092701</v>
+        <v>7092732</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,10 +2564,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467437</v>
+        <v>124467417</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2585,21 +2580,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2609,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514859</v>
+        <v>514963</v>
       </c>
       <c r="R20" t="n">
-        <v>7092793</v>
+        <v>7092735</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2666,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467431</v>
+        <v>124467429</v>
       </c>
       <c r="B21" t="n">
         <v>79891</v>
@@ -2711,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514768</v>
+        <v>514740</v>
       </c>
       <c r="R21" t="n">
-        <v>7092696</v>
+        <v>7092800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,10 +2768,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467439</v>
+        <v>124467441</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2789,21 +2784,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2813,10 +2808,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514824</v>
+        <v>514761</v>
       </c>
       <c r="R22" t="n">
-        <v>7092689</v>
+        <v>7092662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2849,6 +2844,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2875,10 +2875,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467432</v>
+        <v>124467426</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2887,25 +2887,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514748</v>
+        <v>514767</v>
       </c>
       <c r="R23" t="n">
-        <v>7092677</v>
+        <v>7092693</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467434</v>
+        <v>124467435</v>
       </c>
       <c r="B8" t="n">
         <v>79891</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514740</v>
+        <v>514733</v>
       </c>
       <c r="R8" t="n">
-        <v>7092648</v>
+        <v>7092818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467435</v>
+        <v>124467434</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514733</v>
+        <v>514740</v>
       </c>
       <c r="R9" t="n">
-        <v>7092818</v>
+        <v>7092648</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1516,14 +1516,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467433</v>
+        <v>124467421</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1532,34 +1532,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514736</v>
+        <v>514988</v>
       </c>
       <c r="R10" t="n">
-        <v>7092656</v>
+        <v>7092790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1600,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,7 +1631,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467437</v>
+        <v>124467433</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1658,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514859</v>
+        <v>514736</v>
       </c>
       <c r="R11" t="n">
-        <v>7092793</v>
+        <v>7092656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467421</v>
+        <v>124467437</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,42 +1749,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514988</v>
+        <v>514859</v>
       </c>
       <c r="R12" t="n">
-        <v>7092790</v>
+        <v>7092793</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,11 +1809,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467431</v>
+        <v>124467427</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514768</v>
+        <v>514840</v>
       </c>
       <c r="R2" t="n">
-        <v>7092696</v>
+        <v>7092768</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467439</v>
+        <v>124467437</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514824</v>
+        <v>514859</v>
       </c>
       <c r="R3" t="n">
-        <v>7092689</v>
+        <v>7092793</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467438</v>
+        <v>124467442</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514966</v>
+        <v>515001</v>
       </c>
       <c r="R4" t="n">
-        <v>7092776</v>
+        <v>7092701</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467430</v>
+        <v>124467426</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514973</v>
+        <v>514767</v>
       </c>
       <c r="R5" t="n">
-        <v>7092718</v>
+        <v>7092693</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467432</v>
+        <v>124467439</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514748</v>
+        <v>514824</v>
       </c>
       <c r="R6" t="n">
-        <v>7092677</v>
+        <v>7092689</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,14 +1185,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467422</v>
+        <v>124467430</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1201,54 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514980</v>
+        <v>514973</v>
       </c>
       <c r="R7" t="n">
-        <v>7092787</v>
+        <v>7092718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467435</v>
+        <v>124467432</v>
       </c>
       <c r="B8" t="n">
         <v>79891</v>
@@ -1352,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514733</v>
+        <v>514748</v>
       </c>
       <c r="R8" t="n">
-        <v>7092818</v>
+        <v>7092677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,14 +1491,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467421</v>
+        <v>124467441</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1532,42 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514988</v>
+        <v>514761</v>
       </c>
       <c r="R10" t="n">
-        <v>7092790</v>
+        <v>7092662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1571,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467433</v>
+        <v>124467438</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1671,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514736</v>
+        <v>514966</v>
       </c>
       <c r="R11" t="n">
-        <v>7092656</v>
+        <v>7092776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467437</v>
+        <v>124467429</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1773,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514859</v>
+        <v>514740</v>
       </c>
       <c r="R12" t="n">
-        <v>7092793</v>
+        <v>7092800</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467427</v>
+        <v>124467435</v>
       </c>
       <c r="B13" t="n">
         <v>79891</v>
@@ -1875,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514840</v>
+        <v>514733</v>
       </c>
       <c r="R13" t="n">
-        <v>7092768</v>
+        <v>7092818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,14 +1904,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467423</v>
+        <v>124467433</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1953,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514889</v>
+        <v>514736</v>
       </c>
       <c r="R14" t="n">
-        <v>7092670</v>
+        <v>7092656</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,11 +1980,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2044,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467428</v>
+        <v>124467425</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2084,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514789</v>
+        <v>514868</v>
       </c>
       <c r="R15" t="n">
-        <v>7092786</v>
+        <v>7092732</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467442</v>
+        <v>124467431</v>
       </c>
       <c r="B16" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2186,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515001</v>
+        <v>514768</v>
       </c>
       <c r="R16" t="n">
-        <v>7092701</v>
+        <v>7092696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,14 +2210,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467424</v>
+        <v>124467428</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2264,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2288,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514760</v>
+        <v>514789</v>
       </c>
       <c r="R17" t="n">
-        <v>7092670</v>
+        <v>7092786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2324,11 +2286,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2462,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467425</v>
+        <v>124467417</v>
       </c>
       <c r="B19" t="n">
-        <v>91023</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2474,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2502,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514868</v>
+        <v>514963</v>
       </c>
       <c r="R19" t="n">
-        <v>7092732</v>
+        <v>7092735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,14 +2521,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467417</v>
+        <v>124467422</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2580,34 +2537,54 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514963</v>
+        <v>514980</v>
       </c>
       <c r="R20" t="n">
-        <v>7092735</v>
+        <v>7092787</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2640,6 +2617,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2666,14 +2648,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467429</v>
+        <v>124467421</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2682,34 +2664,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514740</v>
+        <v>514988</v>
       </c>
       <c r="R21" t="n">
-        <v>7092800</v>
+        <v>7092790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,6 +2732,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2768,14 +2763,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467441</v>
+        <v>124467424</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2784,21 +2779,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2808,10 +2803,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514761</v>
+        <v>514760</v>
       </c>
       <c r="R22" t="n">
-        <v>7092662</v>
+        <v>7092670</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2848,7 +2843,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2875,37 +2870,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467426</v>
+        <v>124467423</v>
       </c>
       <c r="B23" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2915,10 +2910,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514767</v>
+        <v>514889</v>
       </c>
       <c r="R23" t="n">
-        <v>7092693</v>
+        <v>7092670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2951,6 +2946,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467427</v>
+        <v>124467417</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514840</v>
+        <v>514963</v>
       </c>
       <c r="R2" t="n">
-        <v>7092768</v>
+        <v>7092735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467437</v>
+        <v>124467441</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514859</v>
+        <v>514761</v>
       </c>
       <c r="R3" t="n">
-        <v>7092793</v>
+        <v>7092662</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467442</v>
+        <v>124467434</v>
       </c>
       <c r="B4" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515001</v>
+        <v>514740</v>
       </c>
       <c r="R4" t="n">
-        <v>7092701</v>
+        <v>7092648</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467426</v>
+        <v>124467429</v>
       </c>
       <c r="B5" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514767</v>
+        <v>514740</v>
       </c>
       <c r="R5" t="n">
-        <v>7092693</v>
+        <v>7092800</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467439</v>
+        <v>124467431</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514824</v>
+        <v>514768</v>
       </c>
       <c r="R6" t="n">
-        <v>7092689</v>
+        <v>7092696</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467430</v>
+        <v>124467440</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514973</v>
+        <v>514991</v>
       </c>
       <c r="R7" t="n">
-        <v>7092718</v>
+        <v>7092891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467432</v>
+        <v>124467427</v>
       </c>
       <c r="B8" t="n">
         <v>79891</v>
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514748</v>
+        <v>514840</v>
       </c>
       <c r="R8" t="n">
-        <v>7092677</v>
+        <v>7092768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467434</v>
+        <v>124467439</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514740</v>
+        <v>514824</v>
       </c>
       <c r="R9" t="n">
-        <v>7092648</v>
+        <v>7092689</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467441</v>
+        <v>124467435</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514761</v>
+        <v>514733</v>
       </c>
       <c r="R10" t="n">
-        <v>7092662</v>
+        <v>7092818</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,11 +1577,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467438</v>
+        <v>124467437</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514966</v>
+        <v>514859</v>
       </c>
       <c r="R11" t="n">
-        <v>7092776</v>
+        <v>7092793</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467429</v>
+        <v>124467430</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514740</v>
+        <v>514973</v>
       </c>
       <c r="R12" t="n">
-        <v>7092800</v>
+        <v>7092718</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467435</v>
+        <v>124467425</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514733</v>
+        <v>514868</v>
       </c>
       <c r="R13" t="n">
-        <v>7092818</v>
+        <v>7092732</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467433</v>
+        <v>124467432</v>
       </c>
       <c r="B14" t="n">
         <v>79891</v>
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514736</v>
+        <v>514748</v>
       </c>
       <c r="R14" t="n">
-        <v>7092656</v>
+        <v>7092677</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467425</v>
+        <v>124467426</v>
       </c>
       <c r="B15" t="n">
         <v>91023</v>
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514868</v>
+        <v>514767</v>
       </c>
       <c r="R15" t="n">
-        <v>7092732</v>
+        <v>7092693</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467431</v>
+        <v>124467438</v>
       </c>
       <c r="B16" t="n">
         <v>79891</v>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514768</v>
+        <v>514966</v>
       </c>
       <c r="R16" t="n">
-        <v>7092696</v>
+        <v>7092776</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467428</v>
+        <v>124467442</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514789</v>
+        <v>515001</v>
       </c>
       <c r="R17" t="n">
-        <v>7092786</v>
+        <v>7092701</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467440</v>
+        <v>124467433</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514991</v>
+        <v>514736</v>
       </c>
       <c r="R18" t="n">
-        <v>7092891</v>
+        <v>7092656</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,11 +2393,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467417</v>
+        <v>124467428</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514963</v>
+        <v>514789</v>
       </c>
       <c r="R19" t="n">
-        <v>7092735</v>
+        <v>7092786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,7 +2648,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467421</v>
+        <v>124467424</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2682,24 +2682,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514988</v>
+        <v>514760</v>
       </c>
       <c r="R21" t="n">
-        <v>7092790</v>
+        <v>7092670</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2736,7 +2728,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2763,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467424</v>
+        <v>124467421</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2797,16 +2789,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514760</v>
+        <v>514988</v>
       </c>
       <c r="R22" t="n">
-        <v>7092670</v>
+        <v>7092790</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467440</v>
+        <v>124467427</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514991</v>
+        <v>514840</v>
       </c>
       <c r="R7" t="n">
-        <v>7092891</v>
+        <v>7092768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467427</v>
+        <v>124467440</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514840</v>
+        <v>514991</v>
       </c>
       <c r="R8" t="n">
-        <v>7092768</v>
+        <v>7092891</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467430</v>
+        <v>124467425</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514973</v>
+        <v>514868</v>
       </c>
       <c r="R12" t="n">
-        <v>7092718</v>
+        <v>7092732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467425</v>
+        <v>124467430</v>
       </c>
       <c r="B13" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514868</v>
+        <v>514973</v>
       </c>
       <c r="R13" t="n">
-        <v>7092732</v>
+        <v>7092718</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467417</v>
+        <v>124467428</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514963</v>
+        <v>514789</v>
       </c>
       <c r="R2" t="n">
-        <v>7092735</v>
+        <v>7092786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467441</v>
+        <v>124467435</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514761</v>
+        <v>514733</v>
       </c>
       <c r="R3" t="n">
-        <v>7092662</v>
+        <v>7092818</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467429</v>
+        <v>124467437</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514740</v>
+        <v>514859</v>
       </c>
       <c r="R5" t="n">
-        <v>7092800</v>
+        <v>7092793</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467431</v>
+        <v>124467442</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514768</v>
+        <v>515001</v>
       </c>
       <c r="R6" t="n">
-        <v>7092696</v>
+        <v>7092701</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467427</v>
+        <v>124467438</v>
       </c>
       <c r="B7" t="n">
         <v>79891</v>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514840</v>
+        <v>514966</v>
       </c>
       <c r="R7" t="n">
-        <v>7092768</v>
+        <v>7092776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467440</v>
+        <v>124467426</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514991</v>
+        <v>514767</v>
       </c>
       <c r="R8" t="n">
-        <v>7092891</v>
+        <v>7092693</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467439</v>
+        <v>124467425</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514824</v>
+        <v>514868</v>
       </c>
       <c r="R9" t="n">
-        <v>7092689</v>
+        <v>7092732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467435</v>
+        <v>124467432</v>
       </c>
       <c r="B10" t="n">
         <v>79891</v>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514733</v>
+        <v>514748</v>
       </c>
       <c r="R10" t="n">
-        <v>7092818</v>
+        <v>7092677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467437</v>
+        <v>124467431</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514859</v>
+        <v>514768</v>
       </c>
       <c r="R11" t="n">
-        <v>7092793</v>
+        <v>7092696</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467425</v>
+        <v>124467430</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514868</v>
+        <v>514973</v>
       </c>
       <c r="R12" t="n">
-        <v>7092732</v>
+        <v>7092718</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467430</v>
+        <v>124467440</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514973</v>
+        <v>514991</v>
       </c>
       <c r="R13" t="n">
-        <v>7092718</v>
+        <v>7092891</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467432</v>
+        <v>124467427</v>
       </c>
       <c r="B14" t="n">
         <v>79891</v>
@@ -1949,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514748</v>
+        <v>514840</v>
       </c>
       <c r="R14" t="n">
-        <v>7092677</v>
+        <v>7092768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467426</v>
+        <v>124467417</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514767</v>
+        <v>514963</v>
       </c>
       <c r="R15" t="n">
-        <v>7092693</v>
+        <v>7092735</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467438</v>
+        <v>124467439</v>
       </c>
       <c r="B16" t="n">
         <v>79891</v>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514966</v>
+        <v>514824</v>
       </c>
       <c r="R16" t="n">
-        <v>7092776</v>
+        <v>7092689</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467442</v>
+        <v>124467429</v>
       </c>
       <c r="B17" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515001</v>
+        <v>514740</v>
       </c>
       <c r="R17" t="n">
-        <v>7092701</v>
+        <v>7092800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467428</v>
+        <v>124467441</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514789</v>
+        <v>514761</v>
       </c>
       <c r="R19" t="n">
-        <v>7092786</v>
+        <v>7092662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2495,6 +2490,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467422</v>
+        <v>124467423</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2554,37 +2554,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514980</v>
+        <v>514889</v>
       </c>
       <c r="R20" t="n">
-        <v>7092787</v>
+        <v>7092670</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2621,7 +2601,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,7 +2850,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467423</v>
+        <v>124467422</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2903,17 +2883,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514889</v>
+        <v>514980</v>
       </c>
       <c r="R23" t="n">
-        <v>7092670</v>
+        <v>7092787</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467428</v>
+        <v>124467439</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514789</v>
+        <v>514824</v>
       </c>
       <c r="R2" t="n">
-        <v>7092786</v>
+        <v>7092689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467435</v>
+        <v>124467417</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514733</v>
+        <v>514963</v>
       </c>
       <c r="R3" t="n">
-        <v>7092818</v>
+        <v>7092735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467434</v>
+        <v>124467425</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514740</v>
+        <v>514868</v>
       </c>
       <c r="R4" t="n">
-        <v>7092648</v>
+        <v>7092732</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467437</v>
+        <v>124467432</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514859</v>
+        <v>514748</v>
       </c>
       <c r="R5" t="n">
-        <v>7092793</v>
+        <v>7092677</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467442</v>
+        <v>124467427</v>
       </c>
       <c r="B6" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515001</v>
+        <v>514840</v>
       </c>
       <c r="R6" t="n">
-        <v>7092701</v>
+        <v>7092768</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467438</v>
+        <v>124467430</v>
       </c>
       <c r="B7" t="n">
         <v>79891</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514966</v>
+        <v>514973</v>
       </c>
       <c r="R7" t="n">
-        <v>7092776</v>
+        <v>7092718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467426</v>
+        <v>124467441</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514767</v>
+        <v>514761</v>
       </c>
       <c r="R8" t="n">
-        <v>7092693</v>
+        <v>7092662</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467425</v>
+        <v>124467426</v>
       </c>
       <c r="B9" t="n">
         <v>91023</v>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514868</v>
+        <v>514767</v>
       </c>
       <c r="R9" t="n">
-        <v>7092732</v>
+        <v>7092693</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467432</v>
+        <v>124467442</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514748</v>
+        <v>515001</v>
       </c>
       <c r="R10" t="n">
-        <v>7092677</v>
+        <v>7092701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467431</v>
+        <v>124467433</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514768</v>
+        <v>514736</v>
       </c>
       <c r="R11" t="n">
-        <v>7092696</v>
+        <v>7092656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467430</v>
+        <v>124467435</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514973</v>
+        <v>514733</v>
       </c>
       <c r="R12" t="n">
-        <v>7092718</v>
+        <v>7092818</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467440</v>
+        <v>124467434</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514991</v>
+        <v>514740</v>
       </c>
       <c r="R13" t="n">
-        <v>7092891</v>
+        <v>7092648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467427</v>
+        <v>124467437</v>
       </c>
       <c r="B14" t="n">
         <v>79891</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514840</v>
+        <v>514859</v>
       </c>
       <c r="R14" t="n">
-        <v>7092768</v>
+        <v>7092793</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467417</v>
+        <v>124467431</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514963</v>
+        <v>514768</v>
       </c>
       <c r="R15" t="n">
-        <v>7092735</v>
+        <v>7092696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467439</v>
+        <v>124467428</v>
       </c>
       <c r="B16" t="n">
         <v>79891</v>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514824</v>
+        <v>514789</v>
       </c>
       <c r="R16" t="n">
-        <v>7092689</v>
+        <v>7092786</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467429</v>
+        <v>124467440</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514740</v>
+        <v>514991</v>
       </c>
       <c r="R17" t="n">
-        <v>7092800</v>
+        <v>7092891</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467433</v>
+        <v>124467438</v>
       </c>
       <c r="B18" t="n">
         <v>79891</v>
@@ -2352,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514736</v>
+        <v>514966</v>
       </c>
       <c r="R18" t="n">
-        <v>7092656</v>
+        <v>7092776</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467441</v>
+        <v>124467429</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514761</v>
+        <v>514740</v>
       </c>
       <c r="R19" t="n">
-        <v>7092662</v>
+        <v>7092800</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,11 +2495,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467423</v>
+        <v>124467422</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2554,17 +2554,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514889</v>
+        <v>514980</v>
       </c>
       <c r="R20" t="n">
-        <v>7092670</v>
+        <v>7092787</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2601,7 +2621,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467421</v>
+        <v>124467423</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2769,24 +2789,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514988</v>
+        <v>514889</v>
       </c>
       <c r="R22" t="n">
-        <v>7092790</v>
+        <v>7092670</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2823,7 +2835,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2850,7 +2862,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467422</v>
+        <v>124467421</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2883,37 +2895,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514980</v>
+        <v>514988</v>
       </c>
       <c r="R23" t="n">
-        <v>7092787</v>
+        <v>7092790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467439</v>
+        <v>124467417</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514824</v>
+        <v>514963</v>
       </c>
       <c r="R2" t="n">
-        <v>7092689</v>
+        <v>7092735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467417</v>
+        <v>124467437</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514963</v>
+        <v>514859</v>
       </c>
       <c r="R3" t="n">
-        <v>7092735</v>
+        <v>7092793</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467425</v>
+        <v>124467439</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514868</v>
+        <v>514824</v>
       </c>
       <c r="R4" t="n">
-        <v>7092732</v>
+        <v>7092689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467432</v>
+        <v>124467433</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514748</v>
+        <v>514736</v>
       </c>
       <c r="R5" t="n">
-        <v>7092677</v>
+        <v>7092656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467427</v>
+        <v>124467429</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514840</v>
+        <v>514740</v>
       </c>
       <c r="R6" t="n">
-        <v>7092768</v>
+        <v>7092800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467430</v>
+        <v>124467441</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514973</v>
+        <v>514761</v>
       </c>
       <c r="R7" t="n">
-        <v>7092718</v>
+        <v>7092662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467441</v>
+        <v>124467440</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514761</v>
+        <v>514991</v>
       </c>
       <c r="R8" t="n">
-        <v>7092662</v>
+        <v>7092891</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467426</v>
+        <v>124467438</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514767</v>
+        <v>514966</v>
       </c>
       <c r="R9" t="n">
-        <v>7092693</v>
+        <v>7092776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467442</v>
+        <v>124467431</v>
       </c>
       <c r="B10" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515001</v>
+        <v>514768</v>
       </c>
       <c r="R10" t="n">
-        <v>7092701</v>
+        <v>7092696</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467433</v>
+        <v>124467432</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514736</v>
+        <v>514748</v>
       </c>
       <c r="R11" t="n">
-        <v>7092656</v>
+        <v>7092677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467435</v>
+        <v>124467426</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514733</v>
+        <v>514767</v>
       </c>
       <c r="R12" t="n">
-        <v>7092818</v>
+        <v>7092693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467434</v>
+        <v>124467435</v>
       </c>
       <c r="B13" t="n">
         <v>79891</v>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514740</v>
+        <v>514733</v>
       </c>
       <c r="R13" t="n">
-        <v>7092648</v>
+        <v>7092818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467437</v>
+        <v>124467434</v>
       </c>
       <c r="B14" t="n">
         <v>79891</v>
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514859</v>
+        <v>514740</v>
       </c>
       <c r="R14" t="n">
-        <v>7092793</v>
+        <v>7092648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467431</v>
+        <v>124467430</v>
       </c>
       <c r="B15" t="n">
         <v>79891</v>
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514768</v>
+        <v>514973</v>
       </c>
       <c r="R15" t="n">
-        <v>7092696</v>
+        <v>7092718</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467428</v>
+        <v>124467425</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514789</v>
+        <v>514868</v>
       </c>
       <c r="R16" t="n">
-        <v>7092786</v>
+        <v>7092732</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467440</v>
+        <v>124467428</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514991</v>
+        <v>514789</v>
       </c>
       <c r="R17" t="n">
-        <v>7092891</v>
+        <v>7092786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467438</v>
+        <v>124467442</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514966</v>
+        <v>515001</v>
       </c>
       <c r="R18" t="n">
-        <v>7092776</v>
+        <v>7092701</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467429</v>
+        <v>124467427</v>
       </c>
       <c r="B19" t="n">
         <v>79891</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514740</v>
+        <v>514840</v>
       </c>
       <c r="R19" t="n">
-        <v>7092800</v>
+        <v>7092768</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467422</v>
+        <v>124467423</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2554,37 +2554,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514980</v>
+        <v>514889</v>
       </c>
       <c r="R20" t="n">
-        <v>7092787</v>
+        <v>7092670</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2621,7 +2601,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2648,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467424</v>
+        <v>124467422</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2681,17 +2661,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514760</v>
+        <v>514980</v>
       </c>
       <c r="R21" t="n">
-        <v>7092670</v>
+        <v>7092787</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2755,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467423</v>
+        <v>124467424</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514889</v>
+        <v>514760</v>
       </c>
       <c r="R22" t="n">
         <v>7092670</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467417</v>
+        <v>124467437</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514963</v>
+        <v>514859</v>
       </c>
       <c r="R2" t="n">
-        <v>7092735</v>
+        <v>7092793</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467437</v>
+        <v>124467417</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514859</v>
+        <v>514963</v>
       </c>
       <c r="R3" t="n">
-        <v>7092793</v>
+        <v>7092735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467417</v>
+        <v>124467440</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514963</v>
+        <v>514991</v>
       </c>
       <c r="R3" t="n">
-        <v>7092735</v>
+        <v>7092891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467439</v>
+        <v>124467438</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514824</v>
+        <v>514966</v>
       </c>
       <c r="R4" t="n">
-        <v>7092689</v>
+        <v>7092776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467433</v>
+        <v>124467442</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514736</v>
+        <v>515001</v>
       </c>
       <c r="R5" t="n">
-        <v>7092656</v>
+        <v>7092701</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467429</v>
+        <v>124467417</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514740</v>
+        <v>514963</v>
       </c>
       <c r="R6" t="n">
-        <v>7092800</v>
+        <v>7092735</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467441</v>
+        <v>124467439</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514761</v>
+        <v>514824</v>
       </c>
       <c r="R7" t="n">
-        <v>7092662</v>
+        <v>7092689</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467440</v>
+        <v>124467432</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514991</v>
+        <v>514748</v>
       </c>
       <c r="R8" t="n">
-        <v>7092891</v>
+        <v>7092677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467438</v>
+        <v>124467431</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514966</v>
+        <v>514768</v>
       </c>
       <c r="R9" t="n">
-        <v>7092776</v>
+        <v>7092696</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467431</v>
+        <v>124467430</v>
       </c>
       <c r="B10" t="n">
         <v>79891</v>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514768</v>
+        <v>514973</v>
       </c>
       <c r="R10" t="n">
-        <v>7092696</v>
+        <v>7092718</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467432</v>
+        <v>124467427</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514748</v>
+        <v>514840</v>
       </c>
       <c r="R11" t="n">
-        <v>7092677</v>
+        <v>7092768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467426</v>
+        <v>124467441</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514767</v>
+        <v>514761</v>
       </c>
       <c r="R12" t="n">
-        <v>7092693</v>
+        <v>7092662</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467435</v>
+        <v>124467426</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514733</v>
+        <v>514767</v>
       </c>
       <c r="R13" t="n">
-        <v>7092818</v>
+        <v>7092693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467434</v>
+        <v>124467429</v>
       </c>
       <c r="B14" t="n">
         <v>79891</v>
@@ -1952,7 +1952,7 @@
         <v>514740</v>
       </c>
       <c r="R14" t="n">
-        <v>7092648</v>
+        <v>7092800</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467430</v>
+        <v>124467434</v>
       </c>
       <c r="B15" t="n">
         <v>79891</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514973</v>
+        <v>514740</v>
       </c>
       <c r="R15" t="n">
-        <v>7092718</v>
+        <v>7092648</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467425</v>
+        <v>124467428</v>
       </c>
       <c r="B16" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514868</v>
+        <v>514789</v>
       </c>
       <c r="R16" t="n">
-        <v>7092732</v>
+        <v>7092786</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467428</v>
+        <v>124467433</v>
       </c>
       <c r="B17" t="n">
         <v>79891</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514789</v>
+        <v>514736</v>
       </c>
       <c r="R17" t="n">
-        <v>7092786</v>
+        <v>7092656</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467442</v>
+        <v>124467425</v>
       </c>
       <c r="B18" t="n">
-        <v>91579</v>
+        <v>91023</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>760</v>
+        <v>1205</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515001</v>
+        <v>514868</v>
       </c>
       <c r="R18" t="n">
-        <v>7092701</v>
+        <v>7092732</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467427</v>
+        <v>124467435</v>
       </c>
       <c r="B19" t="n">
         <v>79891</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514840</v>
+        <v>514733</v>
       </c>
       <c r="R19" t="n">
-        <v>7092768</v>
+        <v>7092818</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467423</v>
+        <v>124467422</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2554,17 +2554,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514889</v>
+        <v>514980</v>
       </c>
       <c r="R20" t="n">
-        <v>7092670</v>
+        <v>7092787</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2601,7 +2621,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2628,7 +2648,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467422</v>
+        <v>124467424</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2661,37 +2681,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514980</v>
+        <v>514760</v>
       </c>
       <c r="R21" t="n">
-        <v>7092787</v>
+        <v>7092670</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2755,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467424</v>
+        <v>124467421</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2789,16 +2789,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514760</v>
+        <v>514988</v>
       </c>
       <c r="R22" t="n">
-        <v>7092670</v>
+        <v>7092790</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2835,7 +2843,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,7 +2870,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467421</v>
+        <v>124467423</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2896,24 +2904,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514988</v>
+        <v>514889</v>
       </c>
       <c r="R23" t="n">
-        <v>7092790</v>
+        <v>7092670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467437</v>
+        <v>124467431</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514859</v>
+        <v>514768</v>
       </c>
       <c r="R2" t="n">
-        <v>7092793</v>
+        <v>7092696</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467440</v>
+        <v>124467437</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514991</v>
+        <v>514859</v>
       </c>
       <c r="R3" t="n">
-        <v>7092891</v>
+        <v>7092793</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467442</v>
+        <v>124467440</v>
       </c>
       <c r="B5" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515001</v>
+        <v>514991</v>
       </c>
       <c r="R5" t="n">
-        <v>7092701</v>
+        <v>7092891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467417</v>
+        <v>124467425</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514963</v>
+        <v>514868</v>
       </c>
       <c r="R6" t="n">
-        <v>7092735</v>
+        <v>7092732</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467432</v>
+        <v>124467428</v>
       </c>
       <c r="B8" t="n">
         <v>79891</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514748</v>
+        <v>514789</v>
       </c>
       <c r="R8" t="n">
-        <v>7092677</v>
+        <v>7092786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467431</v>
+        <v>124467442</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514768</v>
+        <v>515001</v>
       </c>
       <c r="R9" t="n">
-        <v>7092696</v>
+        <v>7092701</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467430</v>
+        <v>124467429</v>
       </c>
       <c r="B10" t="n">
         <v>79891</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514973</v>
+        <v>514740</v>
       </c>
       <c r="R10" t="n">
-        <v>7092718</v>
+        <v>7092800</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467427</v>
+        <v>124467432</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514840</v>
+        <v>514748</v>
       </c>
       <c r="R11" t="n">
-        <v>7092768</v>
+        <v>7092677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467441</v>
+        <v>124467427</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514761</v>
+        <v>514840</v>
       </c>
       <c r="R12" t="n">
-        <v>7092662</v>
+        <v>7092768</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467429</v>
+        <v>124467441</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514740</v>
+        <v>514761</v>
       </c>
       <c r="R14" t="n">
-        <v>7092800</v>
+        <v>7092662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,6 +1980,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467428</v>
+        <v>124467417</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514789</v>
+        <v>514963</v>
       </c>
       <c r="R16" t="n">
-        <v>7092786</v>
+        <v>7092735</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467433</v>
+        <v>124467435</v>
       </c>
       <c r="B17" t="n">
         <v>79891</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514736</v>
+        <v>514733</v>
       </c>
       <c r="R17" t="n">
-        <v>7092656</v>
+        <v>7092818</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467425</v>
+        <v>124467430</v>
       </c>
       <c r="B18" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514868</v>
+        <v>514973</v>
       </c>
       <c r="R18" t="n">
-        <v>7092732</v>
+        <v>7092718</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467435</v>
+        <v>124467433</v>
       </c>
       <c r="B19" t="n">
         <v>79891</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514733</v>
+        <v>514736</v>
       </c>
       <c r="R19" t="n">
-        <v>7092818</v>
+        <v>7092656</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467422</v>
+        <v>124467423</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2554,37 +2554,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514980</v>
+        <v>514889</v>
       </c>
       <c r="R20" t="n">
-        <v>7092787</v>
+        <v>7092670</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2621,7 +2601,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2648,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467424</v>
+        <v>124467421</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2682,16 +2662,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514760</v>
+        <v>514988</v>
       </c>
       <c r="R21" t="n">
-        <v>7092670</v>
+        <v>7092790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,7 +2716,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2755,7 +2743,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467421</v>
+        <v>124467424</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2789,24 +2777,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514988</v>
+        <v>514760</v>
       </c>
       <c r="R22" t="n">
-        <v>7092790</v>
+        <v>7092670</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2843,7 +2823,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2870,7 +2850,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467423</v>
+        <v>124467422</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2903,17 +2883,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514889</v>
+        <v>514980</v>
       </c>
       <c r="R23" t="n">
-        <v>7092670</v>
+        <v>7092787</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467431</v>
+        <v>124467435</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514768</v>
+        <v>514733</v>
       </c>
       <c r="R2" t="n">
-        <v>7092696</v>
+        <v>7092818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467437</v>
+        <v>124467430</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514859</v>
+        <v>514973</v>
       </c>
       <c r="R3" t="n">
-        <v>7092793</v>
+        <v>7092718</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467438</v>
+        <v>124467428</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514966</v>
+        <v>514789</v>
       </c>
       <c r="R4" t="n">
-        <v>7092776</v>
+        <v>7092786</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467440</v>
+        <v>124467426</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514991</v>
+        <v>514767</v>
       </c>
       <c r="R5" t="n">
-        <v>7092891</v>
+        <v>7092693</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467425</v>
+        <v>124467431</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514868</v>
+        <v>514768</v>
       </c>
       <c r="R6" t="n">
-        <v>7092732</v>
+        <v>7092696</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467439</v>
+        <v>124467417</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514824</v>
+        <v>514963</v>
       </c>
       <c r="R7" t="n">
-        <v>7092689</v>
+        <v>7092735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467428</v>
+        <v>124467441</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514789</v>
+        <v>514761</v>
       </c>
       <c r="R8" t="n">
-        <v>7092786</v>
+        <v>7092662</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467442</v>
+        <v>124467433</v>
       </c>
       <c r="B9" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515001</v>
+        <v>514736</v>
       </c>
       <c r="R9" t="n">
-        <v>7092701</v>
+        <v>7092656</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467429</v>
+        <v>124467432</v>
       </c>
       <c r="B10" t="n">
         <v>79891</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514740</v>
+        <v>514748</v>
       </c>
       <c r="R10" t="n">
-        <v>7092800</v>
+        <v>7092677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467432</v>
+        <v>124467438</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514748</v>
+        <v>514966</v>
       </c>
       <c r="R11" t="n">
-        <v>7092677</v>
+        <v>7092776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467427</v>
+        <v>124467434</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514840</v>
+        <v>514740</v>
       </c>
       <c r="R12" t="n">
-        <v>7092768</v>
+        <v>7092648</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467426</v>
+        <v>124467427</v>
       </c>
       <c r="B13" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514767</v>
+        <v>514840</v>
       </c>
       <c r="R13" t="n">
-        <v>7092693</v>
+        <v>7092768</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467441</v>
+        <v>124467442</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514761</v>
+        <v>515001</v>
       </c>
       <c r="R14" t="n">
-        <v>7092662</v>
+        <v>7092701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1980,11 +1980,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467434</v>
+        <v>124467440</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514740</v>
+        <v>514991</v>
       </c>
       <c r="R15" t="n">
-        <v>7092648</v>
+        <v>7092891</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467417</v>
+        <v>124467425</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514963</v>
+        <v>514868</v>
       </c>
       <c r="R16" t="n">
-        <v>7092735</v>
+        <v>7092732</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467435</v>
+        <v>124467439</v>
       </c>
       <c r="B17" t="n">
         <v>79891</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514733</v>
+        <v>514824</v>
       </c>
       <c r="R17" t="n">
-        <v>7092818</v>
+        <v>7092689</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467430</v>
+        <v>124467437</v>
       </c>
       <c r="B18" t="n">
         <v>79891</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514973</v>
+        <v>514859</v>
       </c>
       <c r="R18" t="n">
-        <v>7092718</v>
+        <v>7092793</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467433</v>
+        <v>124467429</v>
       </c>
       <c r="B19" t="n">
         <v>79891</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514736</v>
+        <v>514740</v>
       </c>
       <c r="R19" t="n">
-        <v>7092656</v>
+        <v>7092800</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467423</v>
+        <v>124467421</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2555,16 +2555,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514889</v>
+        <v>514988</v>
       </c>
       <c r="R20" t="n">
-        <v>7092670</v>
+        <v>7092790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2601,7 +2609,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2628,7 +2636,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467421</v>
+        <v>124467422</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2661,25 +2669,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514988</v>
+        <v>514980</v>
       </c>
       <c r="R21" t="n">
-        <v>7092790</v>
+        <v>7092787</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,7 +2736,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2743,7 +2763,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467424</v>
+        <v>124467423</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2783,7 +2803,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514760</v>
+        <v>514889</v>
       </c>
       <c r="R22" t="n">
         <v>7092670</v>
@@ -2850,7 +2870,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467422</v>
+        <v>124467424</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2883,37 +2903,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514980</v>
+        <v>514760</v>
       </c>
       <c r="R23" t="n">
-        <v>7092787</v>
+        <v>7092670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467430</v>
+        <v>124467440</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514973</v>
+        <v>514991</v>
       </c>
       <c r="R3" t="n">
-        <v>7092718</v>
+        <v>7092891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467428</v>
+        <v>124467441</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514789</v>
+        <v>514761</v>
       </c>
       <c r="R4" t="n">
-        <v>7092786</v>
+        <v>7092662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124467426</v>
+        <v>124467438</v>
       </c>
       <c r="B5" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514767</v>
+        <v>514966</v>
       </c>
       <c r="R5" t="n">
-        <v>7092693</v>
+        <v>7092776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467431</v>
+        <v>124467429</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514768</v>
+        <v>514740</v>
       </c>
       <c r="R6" t="n">
-        <v>7092696</v>
+        <v>7092800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467417</v>
+        <v>124467442</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91579</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514963</v>
+        <v>515001</v>
       </c>
       <c r="R7" t="n">
-        <v>7092735</v>
+        <v>7092701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467441</v>
+        <v>124467432</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514761</v>
+        <v>514748</v>
       </c>
       <c r="R8" t="n">
-        <v>7092662</v>
+        <v>7092677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467433</v>
+        <v>124467430</v>
       </c>
       <c r="B9" t="n">
         <v>79891</v>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514736</v>
+        <v>514973</v>
       </c>
       <c r="R9" t="n">
-        <v>7092656</v>
+        <v>7092718</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467432</v>
+        <v>124467434</v>
       </c>
       <c r="B10" t="n">
         <v>79891</v>
@@ -1536,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514748</v>
+        <v>514740</v>
       </c>
       <c r="R10" t="n">
-        <v>7092677</v>
+        <v>7092648</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467438</v>
+        <v>124467431</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514966</v>
+        <v>514768</v>
       </c>
       <c r="R11" t="n">
-        <v>7092776</v>
+        <v>7092696</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467434</v>
+        <v>124467428</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514740</v>
+        <v>514789</v>
       </c>
       <c r="R12" t="n">
-        <v>7092648</v>
+        <v>7092786</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467427</v>
+        <v>124467439</v>
       </c>
       <c r="B13" t="n">
         <v>79891</v>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514840</v>
+        <v>514824</v>
       </c>
       <c r="R13" t="n">
-        <v>7092768</v>
+        <v>7092689</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467442</v>
+        <v>124467433</v>
       </c>
       <c r="B14" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515001</v>
+        <v>514736</v>
       </c>
       <c r="R14" t="n">
-        <v>7092701</v>
+        <v>7092656</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467440</v>
+        <v>124467417</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514991</v>
+        <v>514963</v>
       </c>
       <c r="R15" t="n">
-        <v>7092891</v>
+        <v>7092735</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,11 +2087,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467439</v>
+        <v>124467427</v>
       </c>
       <c r="B17" t="n">
         <v>79891</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514824</v>
+        <v>514840</v>
       </c>
       <c r="R17" t="n">
-        <v>7092689</v>
+        <v>7092768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467437</v>
+        <v>124467426</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514859</v>
+        <v>514767</v>
       </c>
       <c r="R18" t="n">
-        <v>7092793</v>
+        <v>7092693</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124467429</v>
+        <v>124467437</v>
       </c>
       <c r="B19" t="n">
         <v>79891</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514740</v>
+        <v>514859</v>
       </c>
       <c r="R19" t="n">
-        <v>7092800</v>
+        <v>7092793</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467435</v>
+        <v>124467440</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514733</v>
+        <v>514991</v>
       </c>
       <c r="R2" t="n">
-        <v>7092818</v>
+        <v>7092891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124467440</v>
+        <v>124467417</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514991</v>
+        <v>514963</v>
       </c>
       <c r="R3" t="n">
-        <v>7092891</v>
+        <v>7092735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467441</v>
+        <v>124467439</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514761</v>
+        <v>514824</v>
       </c>
       <c r="R4" t="n">
-        <v>7092662</v>
+        <v>7092689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124467429</v>
+        <v>124467431</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514740</v>
+        <v>514768</v>
       </c>
       <c r="R6" t="n">
-        <v>7092800</v>
+        <v>7092696</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124467442</v>
+        <v>124467430</v>
       </c>
       <c r="B7" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515001</v>
+        <v>514973</v>
       </c>
       <c r="R7" t="n">
-        <v>7092701</v>
+        <v>7092718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124467432</v>
+        <v>124467442</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514748</v>
+        <v>515001</v>
       </c>
       <c r="R8" t="n">
-        <v>7092677</v>
+        <v>7092701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467430</v>
+        <v>124467425</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514973</v>
+        <v>514868</v>
       </c>
       <c r="R9" t="n">
-        <v>7092718</v>
+        <v>7092732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467434</v>
+        <v>124467441</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514740</v>
+        <v>514761</v>
       </c>
       <c r="R10" t="n">
-        <v>7092648</v>
+        <v>7092662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467431</v>
+        <v>124467427</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514768</v>
+        <v>514840</v>
       </c>
       <c r="R11" t="n">
-        <v>7092696</v>
+        <v>7092768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467439</v>
+        <v>124467433</v>
       </c>
       <c r="B13" t="n">
         <v>79891</v>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514824</v>
+        <v>514736</v>
       </c>
       <c r="R13" t="n">
-        <v>7092689</v>
+        <v>7092656</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467433</v>
+        <v>124467432</v>
       </c>
       <c r="B14" t="n">
         <v>79891</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514736</v>
+        <v>514748</v>
       </c>
       <c r="R14" t="n">
-        <v>7092656</v>
+        <v>7092677</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124467417</v>
+        <v>124467435</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514963</v>
+        <v>514733</v>
       </c>
       <c r="R15" t="n">
-        <v>7092735</v>
+        <v>7092818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467425</v>
+        <v>124467429</v>
       </c>
       <c r="B16" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514868</v>
+        <v>514740</v>
       </c>
       <c r="R16" t="n">
-        <v>7092732</v>
+        <v>7092800</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124467427</v>
+        <v>124467426</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514840</v>
+        <v>514767</v>
       </c>
       <c r="R17" t="n">
-        <v>7092768</v>
+        <v>7092693</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467426</v>
+        <v>124467434</v>
       </c>
       <c r="B18" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514767</v>
+        <v>514740</v>
       </c>
       <c r="R18" t="n">
-        <v>7092693</v>
+        <v>7092648</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467422</v>
+        <v>124467423</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2669,37 +2669,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514980</v>
+        <v>514889</v>
       </c>
       <c r="R21" t="n">
-        <v>7092787</v>
+        <v>7092670</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2736,7 +2716,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2763,7 +2743,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467423</v>
+        <v>124467424</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2803,7 +2783,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514889</v>
+        <v>514760</v>
       </c>
       <c r="R22" t="n">
         <v>7092670</v>
@@ -2870,7 +2850,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467424</v>
+        <v>124467422</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2903,17 +2883,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514760</v>
+        <v>514980</v>
       </c>
       <c r="R23" t="n">
-        <v>7092670</v>
+        <v>7092787</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -2521,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467421</v>
+        <v>124467424</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,24 +2555,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514988</v>
+        <v>514760</v>
       </c>
       <c r="R20" t="n">
-        <v>7092790</v>
+        <v>7092670</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,7 +2601,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467423</v>
+        <v>124467422</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2669,17 +2661,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514889</v>
+        <v>514980</v>
       </c>
       <c r="R21" t="n">
-        <v>7092670</v>
+        <v>7092787</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,7 +2728,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2743,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467424</v>
+        <v>124467423</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2783,7 +2795,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514760</v>
+        <v>514889</v>
       </c>
       <c r="R22" t="n">
         <v>7092670</v>
@@ -2850,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467422</v>
+        <v>124467421</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,37 +2895,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514980</v>
+        <v>514988</v>
       </c>
       <c r="R23" t="n">
-        <v>7092787</v>
+        <v>7092790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 6502-2025 artfynd.xlsx
+++ b/artfynd/A 6502-2025 artfynd.xlsx
@@ -2521,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467424</v>
+        <v>124467423</v>
       </c>
       <c r="B20" t="n">
         <v>57635</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514760</v>
+        <v>514889</v>
       </c>
       <c r="R20" t="n">
         <v>7092670</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467422</v>
+        <v>124467421</v>
       </c>
       <c r="B21" t="n">
         <v>57635</v>
@@ -2661,37 +2661,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514980</v>
+        <v>514988</v>
       </c>
       <c r="R21" t="n">
-        <v>7092787</v>
+        <v>7092790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,7 +2716,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ca 5m upp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2755,7 +2743,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124467423</v>
+        <v>124467422</v>
       </c>
       <c r="B22" t="n">
         <v>57635</v>
@@ -2788,17 +2776,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514889</v>
+        <v>514980</v>
       </c>
       <c r="R22" t="n">
-        <v>7092670</v>
+        <v>7092787</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2835,7 +2843,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,7 +2870,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124467421</v>
+        <v>124467424</v>
       </c>
       <c r="B23" t="n">
         <v>57635</v>
@@ -2896,24 +2904,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Renålandet sö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514988</v>
+        <v>514760</v>
       </c>
       <c r="R23" t="n">
-        <v>7092790</v>
+        <v>7092670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ca 5m upp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
